--- a/output/pdf_financials_xlsx/ALTU.xlsx
+++ b/output/pdf_financials_xlsx/ALTU.xlsx
@@ -1135,10 +1135,10 @@
         <v>-2.508259</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.395226</v>
+        <v>-0.395226</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.084594</v>
+        <v>-1.084594</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.022725</v>
+        <v>-1.864683</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.049692</v>
+        <v>-2.191066</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
         <v>-2.508259</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.395226</v>
+        <v>-0.395226</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.084594</v>
+        <v>-1.084594</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.920979</v>
+        <v>-0.920979</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.070687</v>
+        <v>-1.070687</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
         <v>-2.508259</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.395226</v>
+        <v>-0.395226</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.084594</v>
+        <v>-1.084594</v>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.920979</v>
+        <v>-0.920979</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.070687</v>
+        <v>-1.070687</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-3.818</v>
@@ -1651,10 +1651,10 @@
         <v>25.08259</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.95226</v>
+        <v>-3.95226</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>54.2297</v>
+        <v>-54.2297</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>23.024475</v>
+        <v>-23.024475</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>53.53435</v>
+        <v>-53.53435</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
         <v>-2.508259</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.395226</v>
+        <v>-0.395226</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.084594</v>
+        <v>-1.084594</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1801,10 +1801,10 @@
         <v>-2.488894</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.407945</v>
+        <v>-0.382507</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.093087</v>
+        <v>-1.076101</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1913,10 +1913,10 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2.408064393072404</v>
+        <v>197.5919356069276</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>4.435284845574579</v>
+        <v>195.5647151544254</v>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
@@ -22810,10 +22810,10 @@
         </is>
       </c>
       <c r="G237" s="5" t="n">
-        <v>0.395226</v>
+        <v>-0.395226</v>
       </c>
       <c r="H237" s="5" t="n">
-        <v>1.084594</v>
+        <v>-1.084594</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -22821,10 +22821,10 @@
         </is>
       </c>
       <c r="J237" s="5" t="n">
-        <v>0.920979</v>
+        <v>-0.920979</v>
       </c>
       <c r="K237" s="5" t="n">
-        <v>1.070687</v>
+        <v>-1.070687</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ALTU.xlsx
+++ b/output/pdf_financials_xlsx/ALTU.xlsx
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.019518</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>9.1e-05</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-1.4e-05</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.183584</v>
+        <v>-1.203102</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.508259</v>
+        <v>-2.50835</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.395226</v>
@@ -1715,7 +1715,7 @@
         <v>0.943704</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.120379</v>
+        <v>1.120393</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.156146</v>
+        <v>-1.175664</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.488894</v>
+        <v>-2.488985</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.382507</v>
@@ -1815,7 +1815,7 @@
         <v>0.946831</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.120379</v>
+        <v>1.120393</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -2047,16 +2047,16 @@
         <v>0.00184</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>6.712</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.684</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="35">
@@ -2127,16 +2127,16 @@
         <v>0.00184</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>6.712</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.684</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="37">
@@ -2607,16 +2607,16 @@
         <v>0.085992</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>7.022</v>
+        <v>0.31</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.756</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.104</v>
+        <v>0.019</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.02</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="49">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -21710,7 +21710,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -22508,7 +22508,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -26410,7 +26410,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E289" s="5" t="n">

--- a/output/pdf_financials_xlsx/ALTU.xlsx
+++ b/output/pdf_financials_xlsx/ALTU.xlsx
@@ -540,10 +540,8 @@
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -590,10 +588,8 @@
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -640,10 +636,8 @@
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -690,10 +684,8 @@
       <c r="E7" s="3" t="n">
         <v>0.130801</v>
       </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F7" s="3" t="n">
+        <v>0.037052</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.093726</v>
@@ -740,10 +732,8 @@
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -790,10 +780,8 @@
       <c r="E9" s="3" t="n">
         <v>0.300554</v>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F9" s="3" t="n">
+        <v>0.258725</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0.314059</v>
@@ -840,10 +828,8 @@
       <c r="E10" s="3" t="n">
         <v>0.431355</v>
       </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F10" s="3" t="n">
+        <v>0.295777</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.407785</v>
@@ -890,10 +876,8 @@
       <c r="E11" s="3" t="n">
         <v>-0.431355</v>
       </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F11" s="3" t="n">
+        <v>-0.295777</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-0.407785</v>
@@ -940,10 +924,8 @@
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -990,10 +972,8 @@
       <c r="E13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>-0</v>
@@ -1040,10 +1020,8 @@
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -1090,10 +1068,8 @@
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F15" s="3" t="n">
+        <v>-0.200074</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0.058284</v>
@@ -1138,12 +1114,10 @@
         <v>-0.395226</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-1.084594</v>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.084594</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1.683506</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0.943704</v>
@@ -1188,18 +1162,16 @@
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.169188</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.003426</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-1.864683</v>
+        <v>0.022725</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-2.191066</v>
+        <v>0.049692</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
@@ -1364,10 +1336,8 @@
       <c r="E20" s="3" t="n">
         <v>-1.084594</v>
       </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F20" s="3" t="n">
+        <v>-1.68008</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.920979</v>
@@ -1414,10 +1384,8 @@
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -1464,10 +1432,8 @@
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0</v>
@@ -1514,10 +1480,8 @@
       <c r="E23" s="3" t="n">
         <v>-1.084594</v>
       </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F23" s="3" t="n">
+        <v>-1.68008</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-0.920979</v>
@@ -1554,12 +1518,10 @@
         <v>0.1</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.11</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0.15</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>0.04</v>
@@ -1604,12 +1566,10 @@
         <v>0.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.11</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0.15</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0.04</v>
@@ -1654,12 +1614,10 @@
         <v>-3.95226</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-54.2297</v>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9.859945</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>-11.200533</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>-23.024475</v>
@@ -1704,12 +1662,10 @@
         <v>-0.395226</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.084594</v>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.084594</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1.683506</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0.943704</v>
@@ -1756,10 +1712,8 @@
       <c r="E28" s="3" t="n">
         <v>0.008493000000000001</v>
       </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F28" s="3" t="n">
+        <v>0.004332</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.003127</v>
@@ -1804,12 +1758,10 @@
         <v>-0.382507</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.076101</v>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.093087</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1.687838</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.946831</v>
@@ -1916,18 +1868,16 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>200</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0.2035038782160563</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>197.5919356069276</v>
+        <v>2.408064393072404</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>195.5647151544254</v>
+        <v>4.435284845574579</v>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
@@ -4708,10 +4658,8 @@
       <c r="E99" s="3" t="n">
         <v>-1.084594</v>
       </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="3" t="n">
+        <v>-1.68008</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-0.920979</v>
@@ -4750,10 +4698,8 @@
       <c r="E100" s="3" t="n">
         <v>0.008493000000000001</v>
       </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F100" s="3" t="n">
+        <v>0.004332</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0.003127</v>
@@ -4792,10 +4738,8 @@
       <c r="E101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
@@ -4834,10 +4778,8 @@
       <c r="E102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G102" s="3" t="n">
         <v>0</v>
@@ -4876,10 +4818,8 @@
       <c r="E103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G103" s="3" t="n">
         <v>0</v>
@@ -4918,10 +4858,8 @@
       <c r="E104" s="3" t="n">
         <v>0.176022</v>
       </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F104" s="3" t="n">
+        <v>0.30903</v>
       </c>
       <c r="G104" s="3" t="n">
         <v>0.2825</v>
@@ -4960,10 +4898,8 @@
       <c r="E105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G105" s="3" t="n">
         <v>0</v>
@@ -5002,10 +4938,8 @@
       <c r="E106" s="3" t="n">
         <v>-0.461212</v>
       </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F106" s="3" t="n">
+        <v>-0.186945</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>-0.297205</v>
@@ -5044,10 +4978,8 @@
       <c r="E107" s="3" t="n">
         <v>0.218099</v>
       </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F107" s="3" t="n">
+        <v>0.016947</v>
       </c>
       <c r="G107" s="3" t="n">
         <v>0.04957</v>
@@ -5086,10 +5018,8 @@
       <c r="E108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G108" s="3" t="n">
         <v>0</v>
@@ -5128,10 +5058,8 @@
       <c r="E109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G109" s="3" t="n">
         <v>0</v>
@@ -5170,10 +5098,8 @@
       <c r="E110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -5188,10 +5114,10 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="111">
@@ -5212,10 +5138,8 @@
       <c r="E111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -5254,10 +5178,8 @@
       <c r="E112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -5296,10 +5218,8 @@
       <c r="E113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G113" s="3" t="n">
         <v>0</v>
@@ -5338,10 +5258,8 @@
       <c r="E114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
@@ -5380,10 +5298,8 @@
       <c r="E115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -5422,10 +5338,8 @@
       <c r="E116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
@@ -5464,10 +5378,8 @@
       <c r="E117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G117" s="3" t="n">
         <v>0</v>
@@ -5506,10 +5418,8 @@
       <c r="E118" s="3" t="n">
         <v>-0.427739</v>
       </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F118" s="3" t="n">
+        <v>-0.19253</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0.029786</v>
@@ -5600,10 +5510,8 @@
       <c r="E120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>0</v>
@@ -5642,10 +5550,8 @@
       <c r="E121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
         <v>0</v>
@@ -5684,10 +5590,8 @@
       <c r="E122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G122" s="3" t="n">
         <v>0</v>
@@ -5726,10 +5630,8 @@
       <c r="E123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G123" s="3" t="n">
         <v>0</v>
@@ -5768,10 +5670,8 @@
       <c r="E124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
         <v>0</v>
@@ -5810,10 +5710,8 @@
       <c r="E125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -5852,10 +5750,8 @@
       <c r="E126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G126" s="3" t="n">
         <v>0</v>
@@ -5956,10 +5852,8 @@
       <c r="E128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G128" s="3" t="n">
         <v>0</v>
@@ -6000,10 +5894,8 @@
       <c r="E129" s="3" t="n">
         <v>0.88244</v>
       </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F129" s="3" t="n">
+        <v>0.702035</v>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
@@ -6044,10 +5936,8 @@
       <c r="E130" s="3" t="n">
         <v>0.03246</v>
       </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F130" s="3" t="n">
+        <v>0.018424</v>
       </c>
       <c r="G130" s="3" t="n">
         <v>0.340484</v>
@@ -6094,10 +5984,8 @@
       <c r="E131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G131" s="3" t="n">
         <v>0</v>
@@ -6136,10 +6024,8 @@
       <c r="E132" s="3" t="n">
         <v>-0.006511</v>
       </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F132" s="3" t="n">
+        <v>0.32256</v>
       </c>
       <c r="G132" s="3" t="n">
         <v>-0.338385</v>
@@ -6178,10 +6064,8 @@
       <c r="E133" s="3" t="n">
         <v>0.018424</v>
       </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F133" s="3" t="n">
+        <v>0.340484</v>
       </c>
       <c r="G133" s="3" t="n">
         <v>0.002083</v>
@@ -6228,10 +6112,8 @@
       <c r="E134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -6317,7 +6199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O297"/>
+  <dimension ref="A1:O339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15864,7 +15746,11 @@
           <t>Accretion 9</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -16445,10 +16331,8 @@
       <c r="H145" s="5" t="n">
         <v>-0.461212</v>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I145" s="5" t="n">
+        <v>-0.186945</v>
       </c>
       <c r="J145" s="5" t="n">
         <v>-0.297205</v>
@@ -18861,10 +18745,8 @@
       <c r="H179" s="5" t="n">
         <v>-1.084594</v>
       </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I179" s="5" t="n">
+        <v>-1.68008</v>
       </c>
       <c r="J179" s="5" t="n">
         <v>-0.920979</v>
@@ -18909,7 +18791,11 @@
           <t>Deferred income taxes recovery (note 15)</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -18995,10 +18881,8 @@
       <c r="H181" s="5" t="n">
         <v>0.008493000000000001</v>
       </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I181" s="5" t="n">
+        <v>0.004332</v>
       </c>
       <c r="J181" s="5" t="n">
         <v>0.003127</v>
@@ -19066,10 +18950,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I182" s="5" t="n">
+        <v>-0.200074</v>
       </c>
       <c r="J182" s="5" t="n">
         <v>0.057958</v>
@@ -19559,10 +19441,8 @@
       <c r="H189" s="5" t="n">
         <v>-0.728481</v>
       </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I189" s="5" t="n">
+        <v>-0.46902</v>
       </c>
       <c r="J189" s="5" t="n">
         <v>-0.602027</v>
@@ -19620,10 +19500,8 @@
       <c r="H190" s="5" t="n">
         <v>0.09124699999999999</v>
       </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I190" s="5" t="n">
+        <v>-0.026955</v>
       </c>
       <c r="J190" s="5" t="n">
         <v>0.022322</v>
@@ -19685,10 +19563,8 @@
       <c r="H191" s="5" t="n">
         <v>0.176022</v>
       </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I191" s="5" t="n">
+        <v>0.30903</v>
       </c>
       <c r="J191" s="5" t="n">
         <v>0.2825</v>
@@ -19754,10 +19630,8 @@
       <c r="H192" s="5" t="n">
         <v>-0.427739</v>
       </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I192" s="5" t="n">
+        <v>-0.19253</v>
       </c>
       <c r="J192" s="5" t="n">
         <v>-0.04118</v>
@@ -19963,10 +19837,8 @@
       <c r="H195" s="5" t="n">
         <v>0.88244</v>
       </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I195" s="5" t="n">
+        <v>0.702035</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -20099,10 +19971,8 @@
       <c r="H197" s="5" t="n">
         <v>-0.007525</v>
       </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I197" s="5" t="n">
+        <v>-0.0005</v>
       </c>
       <c r="J197" s="5" t="n">
         <v>-1.6e-05</v>
@@ -20166,10 +20036,8 @@
       <c r="H198" s="5" t="n">
         <v>0.03246</v>
       </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I198" s="5" t="n">
+        <v>0.018424</v>
       </c>
       <c r="J198" s="5" t="n">
         <v>0.340484</v>
@@ -20231,10 +20099,8 @@
       <c r="H199" s="5" t="n">
         <v>0.018424</v>
       </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I199" s="5" t="n">
+        <v>0.340484</v>
       </c>
       <c r="J199" s="5" t="n">
         <v>0.002083</v>
@@ -20343,30 +20209,32 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E201" s="5" t="n">
-        <v>0.096859</v>
-      </c>
-      <c r="F201" s="5" t="n">
-        <v>0.383947</v>
-      </c>
-      <c r="G201" s="5" t="n">
-        <v>-0.000666</v>
-      </c>
-      <c r="H201" s="5" t="n">
-        <v>0.218099</v>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Property investigations</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" s="5" t="n">
+        <v>0.012</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -20412,7 +20280,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Foreign exchange translation</t>
+          <t>Loan interest</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -20426,21 +20294,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G202" s="5" t="n">
-        <v>0.018124</v>
-      </c>
-      <c r="H202" s="5" t="n">
-        <v>0.129521</v>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" s="5" t="n">
+        <v>0.00525</v>
+      </c>
+      <c r="J202" s="5" t="n">
+        <v>0.00525</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -20476,38 +20344,36 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Add items not affecting cash</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Common shares and warrants issued for cash - net</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E203" s="5" t="n">
-        <v>0.365977</v>
+        <v>0.096859</v>
       </c>
       <c r="F203" s="5" t="n">
-        <v>1.610625</v>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.383947</v>
+      </c>
+      <c r="G203" s="5" t="n">
+        <v>-0.000666</v>
       </c>
       <c r="H203" s="5" t="n">
-        <v>0.79244</v>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.218099</v>
+      </c>
+      <c r="I203" s="5" t="n">
+        <v>0.016947</v>
+      </c>
+      <c r="J203" s="5" t="n">
+        <v>0.04957</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -20543,12 +20409,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Add items not affecting cash</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Share subscriptions received in advance</t>
+          <t>Asset dispositions included in operations</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -20567,13 +20433,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H204" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" s="5" t="n">
+        <v>0.012483</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -20614,12 +20480,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Add items not affecting cash</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Loan payable</t>
+          <t>Writedowns</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -20633,23 +20499,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G205" s="5" t="n">
-        <v>0.175</v>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I205" s="5" t="n">
+        <v>1.363548</v>
+      </c>
+      <c r="J205" s="5" t="n">
+        <v>0.070966</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -20685,12 +20549,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Add items not affecting cash</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Cash paid during the year for income taxes</t>
+          <t>Loss on debt settlement</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -20719,10 +20583,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J206" s="5" t="n">
+        <v>0.128886</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
@@ -20763,15 +20625,23 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Write-off of mineral properties</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" s="5" t="n">
-        <v>0.062453</v>
-      </c>
-      <c r="F207" s="5" t="n">
-        <v>1.464415</v>
+          <t>Deferred tax recovery</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -20783,15 +20653,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I207" s="5" t="n">
+        <v>-0.003426</v>
+      </c>
+      <c r="J207" s="5" t="n">
+        <v>-0.022725</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
@@ -20827,33 +20693,37 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Cash flows from investing activities</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Mineral properties</t>
+          <t>Common shares and warrants issued for cash – net</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" s="5" t="n">
-        <v>-1.555224</v>
-      </c>
-      <c r="F208" s="5" t="n">
-        <v>-0.58917</v>
-      </c>
-      <c r="G208" s="5" t="n">
-        <v>-0.265448</v>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I208" s="5" t="n">
+        <v>0.548176</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -20899,32 +20769,30 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E209" s="5" t="n">
-        <v>-2.240378</v>
-      </c>
-      <c r="F209" s="5" t="n">
-        <v>0.492002</v>
-      </c>
-      <c r="G209" s="5" t="n">
-        <v>-0.552935</v>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share subscriptions received in advance</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>0.153859</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -20965,42 +20833,36 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Cash flows from investing activities</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Acquisition of capital assets</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
+          <t>Increase (decrease) in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E210" s="5" t="n">
-        <v>-0.004088</v>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.240378</v>
+      </c>
+      <c r="F210" s="5" t="n">
+        <v>0.492002</v>
+      </c>
+      <c r="G210" s="5" t="n">
+        <v>-0.552935</v>
+      </c>
+      <c r="H210" s="5" t="n">
+        <v>-0.006511</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="J210" s="5" t="n">
+        <v>-0.338385</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -21036,39 +20898,33 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Cash flows from investing activities</t>
+          <t>Add items not affecting cash</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Cash flows from investing activities total</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E211" s="5" t="n">
-        <v>-1.559312</v>
-      </c>
-      <c r="F211" s="5" t="n">
-        <v>-0.58917</v>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Foreign exchange translation</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" s="5" t="n">
+        <v>0.018124</v>
+      </c>
+      <c r="H211" s="5" t="n">
+        <v>0.129521</v>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>-0.200074</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -21104,42 +20960,46 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Accounting and audit</t>
+          <t>Common shares and warrants issued for cash - net</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" s="5" t="n">
-        <v>0.096369</v>
+        <v>0.365977</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0.09968</v>
-      </c>
-      <c r="G212" s="5" t="n">
-        <v>0.07568900000000001</v>
+        <v>1.610625</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H212" s="5" t="n">
-        <v>0.110308</v>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J212" s="5" t="n">
-        <v>0.045664</v>
-      </c>
-      <c r="K212" s="5" t="n">
-        <v>0.038646</v>
+        <v>0.79244</v>
+      </c>
+      <c r="I212" s="5" t="n">
+        <v>0.548176</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -21165,42 +21025,52 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Business development</t>
+          <t>Loan payable</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
-      <c r="E213" s="5" t="n">
-        <v>0.008156999999999999</v>
-      </c>
-      <c r="F213" s="5" t="n">
-        <v>0.005522</v>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>0.00387</v>
-      </c>
-      <c r="H213" s="5" t="n">
-        <v>0.0009790000000000001</v>
+        <v>0.175</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J213" s="5" t="n">
-        <v>0.004886</v>
-      </c>
-      <c r="K213" s="5" t="n">
-        <v>0.016435</v>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -21226,43 +21096,49 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Depreciation and amortization</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E214" s="5" t="n">
-        <v>0.027438</v>
-      </c>
-      <c r="F214" s="5" t="n">
-        <v>0.019365</v>
-      </c>
-      <c r="G214" s="5" t="n">
-        <v>0.012719</v>
-      </c>
-      <c r="H214" s="5" t="n">
-        <v>0.008493000000000001</v>
+          <t>Cash paid during the year for income taxes</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J214" s="5" t="n">
-        <v>0.003127</v>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
@@ -21293,42 +21169,50 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Add items not affecting cash</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Dues and fees</t>
+          <t>Write-off of mineral properties</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
       <c r="E215" s="5" t="n">
-        <v>0.003651</v>
+        <v>0.062453</v>
       </c>
       <c r="F215" s="5" t="n">
-        <v>0.004739</v>
-      </c>
-      <c r="G215" s="5" t="n">
-        <v>0.004945</v>
-      </c>
-      <c r="H215" s="5" t="n">
-        <v>0.0044</v>
+        <v>1.464415</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J215" s="5" t="n">
-        <v>0.002513</v>
-      </c>
-      <c r="K215" s="5" t="n">
-        <v>0.001679</v>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -21354,38 +21238,28 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (note 12)</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Mineral properties</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" s="5" t="n">
+        <v>-1.555224</v>
+      </c>
+      <c r="F216" s="5" t="n">
+        <v>-0.58917</v>
+      </c>
+      <c r="G216" s="5" t="n">
+        <v>-0.265448</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -21397,8 +21271,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J216" s="5" t="n">
-        <v>0.058284</v>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -21429,46 +21305,52 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Acquisition of capital assets</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
       <c r="E217" s="5" t="n">
-        <v>0.0183</v>
-      </c>
-      <c r="F217" s="5" t="n">
-        <v>0.016651</v>
-      </c>
-      <c r="G217" s="5" t="n">
-        <v>0.016718</v>
-      </c>
-      <c r="H217" s="5" t="n">
-        <v>0.019491</v>
+        <v>-0.004088</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J217" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="K217" s="5" t="n">
-        <v>0.006425</v>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -21494,29 +21376,29 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Investment expenses</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash flows from investing activities total</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="n">
+        <v>-1.559312</v>
+      </c>
+      <c r="F218" s="5" t="n">
+        <v>-0.58917</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -21533,8 +21415,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J218" s="5" t="n">
-        <v>0.029772</v>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -21575,36 +21459,30 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accounting and audit</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
       <c r="E219" s="5" t="n">
-        <v>0.056967</v>
+        <v>0.096369</v>
       </c>
       <c r="F219" s="5" t="n">
-        <v>0.005799</v>
+        <v>0.09968</v>
       </c>
       <c r="G219" s="5" t="n">
-        <v>0.001638</v>
+        <v>0.07568900000000001</v>
       </c>
       <c r="H219" s="5" t="n">
-        <v>0.090156</v>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.110308</v>
+      </c>
+      <c r="I219" s="5" t="n">
+        <v>0.07884099999999999</v>
       </c>
       <c r="J219" s="5" t="n">
-        <v>0.054527</v>
+        <v>0.045664</v>
       </c>
       <c r="K219" s="5" t="n">
-        <v>0.121083</v>
+        <v>0.038646</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -21640,36 +21518,30 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Business development</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
       <c r="E220" s="5" t="n">
-        <v>0.059321</v>
+        <v>0.008156999999999999</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>0.228509</v>
+        <v>0.005522</v>
       </c>
       <c r="G220" s="5" t="n">
-        <v>0.012925</v>
+        <v>0.00387</v>
       </c>
       <c r="H220" s="5" t="n">
-        <v>0.03678</v>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0009790000000000001</v>
+      </c>
+      <c r="I220" s="5" t="n">
+        <v>0.0017</v>
       </c>
       <c r="J220" s="5" t="n">
-        <v>0.212519</v>
+        <v>0.004886</v>
       </c>
       <c r="K220" s="5" t="n">
-        <v>0.000155</v>
+        <v>0.016435</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -21705,41 +21577,31 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Loan interest expense</t>
+          <t>Depreciation and amortization</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="n">
+        <v>0.027438</v>
+      </c>
+      <c r="F221" s="5" t="n">
+        <v>0.019365</v>
+      </c>
+      <c r="G221" s="5" t="n">
+        <v>0.012719</v>
+      </c>
+      <c r="H221" s="5" t="n">
+        <v>0.008493000000000001</v>
+      </c>
+      <c r="I221" s="5" t="n">
+        <v>0.004332</v>
       </c>
       <c r="J221" s="5" t="n">
-        <v>0.00525</v>
+        <v>0.003127</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -21780,42 +21642,30 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Loss on debt settlement (note 7)</t>
+          <t>Dues and fees</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E222" s="5" t="n">
+        <v>0.003651</v>
+      </c>
+      <c r="F222" s="5" t="n">
+        <v>0.004739</v>
+      </c>
+      <c r="G222" s="5" t="n">
+        <v>0.004945</v>
+      </c>
+      <c r="H222" s="5" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="I222" s="5" t="n">
+        <v>0.001918</v>
       </c>
       <c r="J222" s="5" t="n">
-        <v>0.128886</v>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002513</v>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>0.001679</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -21851,25 +21701,33 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Office and general</t>
+          <t>Foreign exchange loss (note 12)</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E223" s="5" t="n">
-        <v>0.08396199999999999</v>
-      </c>
-      <c r="F223" s="5" t="n">
-        <v>0.017234</v>
-      </c>
-      <c r="G223" s="5" t="n">
-        <v>0.019442</v>
-      </c>
-      <c r="H223" s="5" t="n">
-        <v>0.021154</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -21877,10 +21735,12 @@
         </is>
       </c>
       <c r="J223" s="5" t="n">
-        <v>0.024199</v>
-      </c>
-      <c r="K223" s="5" t="n">
-        <v>0.050761</v>
+        <v>0.058284</v>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -21916,32 +21776,34 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Premises</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E224" s="5" t="n">
-        <v>0.06884999999999999</v>
+        <v>0.0183</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>0.07481599999999999</v>
+        <v>0.016651</v>
       </c>
       <c r="G224" s="5" t="n">
-        <v>0.073889</v>
+        <v>0.016718</v>
       </c>
       <c r="H224" s="5" t="n">
-        <v>0.07057099999999999</v>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.019491</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>0.015674</v>
       </c>
       <c r="J224" s="5" t="n">
-        <v>0.043197</v>
+        <v>0.015</v>
       </c>
       <c r="K224" s="5" t="n">
-        <v>0.043806</v>
+        <v>0.006425</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -21977,21 +21839,29 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Property investigations</t>
+          <t>Investment expenses</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
-      <c r="E225" s="5" t="n">
-        <v>0.050568</v>
-      </c>
-      <c r="F225" s="5" t="n">
-        <v>0.119744</v>
-      </c>
-      <c r="G225" s="5" t="n">
-        <v>-0.022399</v>
-      </c>
-      <c r="H225" s="5" t="n">
-        <v>0.070953</v>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -21999,10 +21869,12 @@
         </is>
       </c>
       <c r="J225" s="5" t="n">
-        <v>0.035775</v>
-      </c>
-      <c r="K225" s="5" t="n">
-        <v>0.004757</v>
+        <v>0.029772</v>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -22038,36 +21910,34 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Regulatory and transfer agent</t>
+          <t>Investor relations</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E226" s="5" t="n">
-        <v>0.01922</v>
+        <v>0.056967</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>0.02901</v>
+        <v>0.005799</v>
       </c>
       <c r="G226" s="5" t="n">
-        <v>0.016138</v>
+        <v>0.001638</v>
       </c>
       <c r="H226" s="5" t="n">
-        <v>0.031521</v>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.090156</v>
+      </c>
+      <c r="I226" s="5" t="n">
+        <v>0.014238</v>
       </c>
       <c r="J226" s="5" t="n">
-        <v>0.02054</v>
+        <v>0.054527</v>
       </c>
       <c r="K226" s="5" t="n">
-        <v>0.014239</v>
+        <v>0.121083</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -22103,7 +21973,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Salaries and benefits</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -22112,27 +21982,25 @@
         </is>
       </c>
       <c r="E227" s="5" t="n">
-        <v>0.451212</v>
+        <v>0.059321</v>
       </c>
       <c r="F227" s="5" t="n">
-        <v>0.448889</v>
+        <v>0.228509</v>
       </c>
       <c r="G227" s="5" t="n">
-        <v>0.127573</v>
+        <v>0.012925</v>
       </c>
       <c r="H227" s="5" t="n">
-        <v>0.232253</v>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.03678</v>
+      </c>
+      <c r="I227" s="5" t="n">
+        <v>0.115858</v>
       </c>
       <c r="J227" s="5" t="n">
-        <v>0.081</v>
+        <v>0.212519</v>
       </c>
       <c r="K227" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.000155</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -22168,10 +22036,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 7)</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>Loan interest expense</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -22198,10 +22070,12 @@
         </is>
       </c>
       <c r="J228" s="5" t="n">
-        <v>0.04957</v>
-      </c>
-      <c r="K228" s="5" t="n">
-        <v>0.143873</v>
+        <v>0.00525</v>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -22237,21 +22111,29 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Loss on debt settlement (note 7)</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
-      <c r="E229" s="5" t="n">
-        <v>0.028307</v>
-      </c>
-      <c r="F229" s="5" t="n">
-        <v>0.0116</v>
-      </c>
-      <c r="G229" s="5" t="n">
-        <v>0.00768</v>
-      </c>
-      <c r="H229" s="5" t="n">
-        <v>0.007223</v>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -22259,10 +22141,12 @@
         </is>
       </c>
       <c r="J229" s="5" t="n">
-        <v>0.012302</v>
-      </c>
-      <c r="K229" s="5" t="n">
-        <v>0.00688</v>
+        <v>0.128886</v>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -22298,32 +22182,34 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Travel and accommodation</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
+          <t>Office and general</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E230" s="5" t="n">
-        <v>0.07145600000000001</v>
+        <v>0.08396199999999999</v>
       </c>
       <c r="F230" s="5" t="n">
-        <v>0.021811</v>
+        <v>0.017234</v>
       </c>
       <c r="G230" s="5" t="n">
-        <v>0.025466</v>
+        <v>0.019442</v>
       </c>
       <c r="H230" s="5" t="n">
-        <v>0.027413</v>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.021154</v>
+      </c>
+      <c r="I230" s="5" t="n">
+        <v>0.021378</v>
       </c>
       <c r="J230" s="5" t="n">
-        <v>0.045727</v>
+        <v>0.024199</v>
       </c>
       <c r="K230" s="5" t="n">
-        <v>0.011309</v>
+        <v>0.050761</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -22359,42 +22245,30 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Impairment of investment available for sale (note 4)</t>
+          <t>Premises</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E231" s="5" t="n">
+        <v>0.06884999999999999</v>
+      </c>
+      <c r="F231" s="5" t="n">
+        <v>0.07481599999999999</v>
+      </c>
+      <c r="G231" s="5" t="n">
+        <v>0.073889</v>
+      </c>
+      <c r="H231" s="5" t="n">
+        <v>0.07057099999999999</v>
+      </c>
+      <c r="I231" s="5" t="n">
+        <v>0.053234</v>
+      </c>
+      <c r="J231" s="5" t="n">
+        <v>0.043197</v>
       </c>
       <c r="K231" s="5" t="n">
-        <v>0.27157</v>
+        <v>0.043806</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -22430,44 +22304,30 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Writedowns (notes 3 and 5)</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>WriteDown</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Property investigations</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" s="5" t="n">
+        <v>0.050568</v>
+      </c>
+      <c r="F232" s="5" t="n">
+        <v>0.119744</v>
+      </c>
+      <c r="G232" s="5" t="n">
+        <v>-0.022399</v>
+      </c>
+      <c r="H232" s="5" t="n">
+        <v>0.070953</v>
+      </c>
+      <c r="I232" s="5" t="n">
+        <v>0.0192</v>
       </c>
       <c r="J232" s="5" t="n">
-        <v>0.070966</v>
+        <v>0.035775</v>
       </c>
       <c r="K232" s="5" t="n">
-        <v>0.394804</v>
+        <v>0.004757</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -22503,46 +22363,34 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Regulatory and transfer agent</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E233" s="5" t="n">
+        <v>0.01922</v>
+      </c>
+      <c r="F233" s="5" t="n">
+        <v>0.02901</v>
+      </c>
+      <c r="G233" s="5" t="n">
+        <v>0.016138</v>
+      </c>
+      <c r="H233" s="5" t="n">
+        <v>0.031521</v>
+      </c>
+      <c r="I233" s="5" t="n">
+        <v>0.028336</v>
+      </c>
+      <c r="J233" s="5" t="n">
+        <v>0.02054</v>
       </c>
       <c r="K233" s="5" t="n">
-        <v>-1.4e-05</v>
+        <v>0.014239</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -22578,42 +22426,34 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Tax credit on abandoned property</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Salaries and benefits</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E234" s="5" t="n">
+        <v>0.451212</v>
+      </c>
+      <c r="F234" s="5" t="n">
+        <v>0.448889</v>
+      </c>
+      <c r="G234" s="5" t="n">
+        <v>0.127573</v>
+      </c>
+      <c r="H234" s="5" t="n">
+        <v>0.232253</v>
+      </c>
+      <c r="I234" s="5" t="n">
+        <v>0.114531</v>
+      </c>
+      <c r="J234" s="5" t="n">
+        <v>0.081</v>
       </c>
       <c r="K234" s="5" t="n">
-        <v>-0.008529</v>
+        <v>0.0025</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -22649,14 +22489,10 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Net loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Stock-based compensation (note 7)</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -22683,10 +22519,10 @@
         </is>
       </c>
       <c r="J235" s="5" t="n">
-        <v>0.943704</v>
+        <v>0.04957</v>
       </c>
       <c r="K235" s="5" t="n">
-        <v>1.120379</v>
+        <v>0.143873</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -22722,40 +22558,30 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (note 15)</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E236" s="5" t="n">
+        <v>0.028307</v>
+      </c>
+      <c r="F236" s="5" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="G236" s="5" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="H236" s="5" t="n">
+        <v>0.007223</v>
+      </c>
+      <c r="I236" s="5" t="n">
+        <v>0.008092999999999999</v>
       </c>
       <c r="J236" s="5" t="n">
-        <v>-0.022725</v>
+        <v>0.012302</v>
       </c>
       <c r="K236" s="5" t="n">
-        <v>-0.049692</v>
+        <v>0.00688</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -22791,40 +22617,30 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Travel and accommodation</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" s="5" t="n">
+        <v>0.07145600000000001</v>
+      </c>
+      <c r="F237" s="5" t="n">
+        <v>0.021811</v>
       </c>
       <c r="G237" s="5" t="n">
-        <v>-0.395226</v>
+        <v>0.025466</v>
       </c>
       <c r="H237" s="5" t="n">
-        <v>-1.084594</v>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.027413</v>
+      </c>
+      <c r="I237" s="5" t="n">
+        <v>0.020502</v>
       </c>
       <c r="J237" s="5" t="n">
-        <v>-0.920979</v>
+        <v>0.045727</v>
       </c>
       <c r="K237" s="5" t="n">
-        <v>-1.070687</v>
+        <v>0.011309</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -22855,12 +22671,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Other comprehensive items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Currency translation adjustment</t>
+          <t>Impairment of investment available for sale (note 4)</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -22889,11 +22705,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J238" s="5" t="n">
-        <v>-0.061457</v>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K238" s="5" t="n">
-        <v>0.010418</v>
+        <v>0.27157</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -22924,15 +22742,19 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Other comprehensive items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Investment available for sale reclassified to loss</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>Writedowns (notes 3 and 5)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>WriteDown</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -22958,13 +22780,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J239" s="5" t="n">
+        <v>0.070966</v>
       </c>
       <c r="K239" s="5" t="n">
-        <v>-0.018299</v>
+        <v>0.394804</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -22995,15 +22815,19 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Other comprehensive items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Unrealized loss on investment available for sale</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -23029,13 +22853,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J240" s="5" t="n">
-        <v>0.018299</v>
-      </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>-1.4e-05</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -23066,12 +22890,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Other comprehensive items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Other comprehensive items total</t>
+          <t>Tax credit on abandoned property</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -23100,11 +22924,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J241" s="5" t="n">
-        <v>-0.043158</v>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K241" s="5" t="n">
-        <v>-0.007881000000000001</v>
+        <v>-0.008529</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -23135,15 +22961,19 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Other comprehensive items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Total comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>Net loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -23159,21 +22989,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H242" s="5" t="n">
+        <v>1.084594</v>
+      </c>
+      <c r="I242" s="5" t="n">
+        <v>1.683506</v>
       </c>
       <c r="J242" s="5" t="n">
-        <v>0.877821</v>
+        <v>0.943704</v>
       </c>
       <c r="K242" s="5" t="n">
-        <v>1.062806</v>
+        <v>1.120379</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -23204,17 +23030,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Other comprehensive items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share (note 7)</t>
+          <t>Deferred income tax recovery (note 15)</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -23243,10 +23069,10 @@
         </is>
       </c>
       <c r="J243" s="5" t="n">
-        <v>4e-08</v>
+        <v>-0.022725</v>
       </c>
       <c r="K243" s="5" t="n">
-        <v>2e-08</v>
+        <v>-0.049692</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -23277,17 +23103,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Other comprehensive items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding (note 7)</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -23300,26 +23126,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G244" s="5" t="n">
+        <v>-0.395226</v>
+      </c>
+      <c r="H244" s="5" t="n">
+        <v>-1.084594</v>
+      </c>
+      <c r="I244" s="5" t="n">
+        <v>-1.68008</v>
       </c>
       <c r="J244" s="5" t="n">
-        <v>23.627543</v>
+        <v>-0.920979</v>
       </c>
       <c r="K244" s="5" t="n">
-        <v>44.990284</v>
+        <v>-1.070687</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -23350,12 +23170,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Common Shares      Contributed  Reserve  Comprehen-                holders’</t>
+          <t>Other comprehensive items</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2013 19,868,798 5,724,380 2,110,446 243,859 (38,617)</t>
+          <t>Currency translation adjustment</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -23379,16 +23199,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I245" s="5" t="n">
+        <v>0.116794</v>
       </c>
       <c r="J245" s="5" t="n">
-        <v>0.486693</v>
+        <v>-0.061457</v>
       </c>
       <c r="K245" s="5" t="n">
-        <v>-7.553375</v>
+        <v>0.010418</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -23419,12 +23237,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Common Shares      Contributed  Reserve  Comprehen-                holders’</t>
+          <t>Other comprehensive items</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Debts to be settled with equity</t>
+          <t>Investment available for sale reclassified to loss</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -23453,11 +23271,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J246" s="5" t="n">
-        <v>0.080176</v>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K246" s="5" t="n">
-        <v>0.080176</v>
+        <v>-0.018299</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -23488,12 +23308,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Common Shares      Contributed  Reserve  Comprehen-                holders’</t>
+          <t>Other comprehensive items</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Shares issued for debt settlement 4,680,692</t>
+          <t>Unrealized loss on investment available for sale</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -23523,10 +23343,12 @@
         </is>
       </c>
       <c r="J247" s="5" t="n">
-        <v>0.280842</v>
-      </c>
-      <c r="K247" s="5" t="n">
-        <v>0.280842</v>
+        <v>0.018299</v>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -23557,12 +23379,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Common Shares      Contributed  Reserve  Comprehen-                holders’</t>
+          <t>Other comprehensive items</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Units issued for debt settlement 1,800,000 108,000</t>
+          <t>Other comprehensive items total</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -23586,16 +23408,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I248" s="5" t="n">
+        <v>0.116794</v>
       </c>
       <c r="J248" s="5" t="n">
-        <v>0.17208</v>
+        <v>-0.043158</v>
       </c>
       <c r="K248" s="5" t="n">
-        <v>0.06408</v>
+        <v>-0.007881000000000001</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -23626,12 +23446,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Common Shares      Contributed  Reserve  Comprehen-                holders’</t>
+          <t>Other comprehensive items</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Equity issued for reserve</t>
+          <t>Total comprehensive loss</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -23655,16 +23475,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I249" s="5" t="n">
+        <v>1.796874</v>
       </c>
       <c r="J249" s="5" t="n">
-        <v>-0.324035</v>
+        <v>0.877821</v>
       </c>
       <c r="K249" s="5" t="n">
-        <v>-0.324035</v>
+        <v>1.062806</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -23695,15 +23513,19 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Common Shares      Contributed  Reserve  Comprehen-                holders’</t>
+          <t>Other comprehensive items</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Shares issued for GRIT investment 5,400,000</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>Basic and diluted loss per share (note 7)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -23730,10 +23552,10 @@
         </is>
       </c>
       <c r="J250" s="5" t="n">
-        <v>0.324</v>
+        <v>4e-08</v>
       </c>
       <c r="K250" s="5" t="n">
-        <v>0.324</v>
+        <v>2e-08</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -23764,15 +23586,19 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Common Shares      Contributed  Reserve  Comprehen-                holders’</t>
+          <t>Other comprehensive items</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Shares issued as finder’s fee 432,000</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding (note 7)</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -23799,10 +23625,10 @@
         </is>
       </c>
       <c r="J251" s="5" t="n">
-        <v>0.02592</v>
+        <v>23.627543</v>
       </c>
       <c r="K251" s="5" t="n">
-        <v>0.02592</v>
+        <v>44.990284</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -23838,7 +23664,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Share-based payment - options</t>
+          <t>Balance, March 31, 2013 19,868,798 5,724,380 2,110,446 243,859 (38,617)</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -23868,10 +23694,10 @@
         </is>
       </c>
       <c r="J252" s="5" t="n">
-        <v>0.05633</v>
+        <v>0.486693</v>
       </c>
       <c r="K252" s="5" t="n">
-        <v>0.05633</v>
+        <v>-7.553375</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -23907,7 +23733,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Other comprehensive items</t>
+          <t>Debts to be settled with equity</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -23937,10 +23763,10 @@
         </is>
       </c>
       <c r="J253" s="5" t="n">
-        <v>0.043158</v>
+        <v>0.080176</v>
       </c>
       <c r="K253" s="5" t="n">
-        <v>0.043158</v>
+        <v>0.080176</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -23976,14 +23802,10 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Shares issued for debt settlement 4,680,692</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -24010,10 +23832,10 @@
         </is>
       </c>
       <c r="J254" s="5" t="n">
-        <v>-0.920979</v>
+        <v>0.280842</v>
       </c>
       <c r="K254" s="5" t="n">
-        <v>-0.920979</v>
+        <v>0.280842</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -24049,7 +23871,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2014 32,181,490 6,463,142 2,230,856 - 4,541</t>
+          <t>Units issued for debt settlement 1,800,000 108,000</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -24079,10 +23901,10 @@
         </is>
       </c>
       <c r="J255" s="5" t="n">
-        <v>0.224185</v>
+        <v>0.17208</v>
       </c>
       <c r="K255" s="5" t="n">
-        <v>-8.474354</v>
+        <v>0.06408</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -24118,7 +23940,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Share-based payment – Iron Range 1,000,000</t>
+          <t>Equity issued for reserve</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -24148,10 +23970,10 @@
         </is>
       </c>
       <c r="J256" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.324035</v>
       </c>
       <c r="K256" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.324035</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -24187,7 +24009,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Non-flow through units issued 7,780,000 225,150</t>
+          <t>Shares issued for GRIT investment 5,400,000</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -24217,10 +24039,10 @@
         </is>
       </c>
       <c r="J257" s="5" t="n">
-        <v>0.389</v>
+        <v>0.324</v>
       </c>
       <c r="K257" s="5" t="n">
-        <v>0.16385</v>
+        <v>0.324</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -24256,7 +24078,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Flow through units issued 4,990,000 142,315</t>
+          <t>Shares issued as finder’s fee 432,000</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -24286,10 +24108,10 @@
         </is>
       </c>
       <c r="J258" s="5" t="n">
-        <v>0.195908</v>
+        <v>0.02592</v>
       </c>
       <c r="K258" s="5" t="n">
-        <v>0.053593</v>
+        <v>0.02592</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -24325,7 +24147,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Warrants issued as finders’ fees</t>
+          <t>Share-based payment - options</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -24355,10 +24177,10 @@
         </is>
       </c>
       <c r="J259" s="5" t="n">
-        <v>0.008869</v>
+        <v>0.05633</v>
       </c>
       <c r="K259" s="5" t="n">
-        <v>0.008869</v>
+        <v>0.05633</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -24394,7 +24216,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Other financing costs (26,623)</t>
+          <t>Other comprehensive items</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -24424,10 +24246,10 @@
         </is>
       </c>
       <c r="J260" s="5" t="n">
-        <v>-0.04217</v>
+        <v>0.043158</v>
       </c>
       <c r="K260" s="5" t="n">
-        <v>-0.015548</v>
+        <v>0.043158</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -24463,10 +24285,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2015 45,951,490 6,873,984 2,632,071 - 12,422</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -24493,10 +24319,10 @@
         </is>
       </c>
       <c r="J261" s="5" t="n">
-        <v>-0.026564</v>
+        <v>-0.920979</v>
       </c>
       <c r="K261" s="5" t="n">
-        <v>-9.545040999999999</v>
+        <v>-0.920979</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -24527,12 +24353,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Common Shares      Contributed  Reserve  Comprehen-                holders’</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Foreign exchange translation (note 9)</t>
+          <t>Balance, March 31, 2014 32,181,490 6,463,142 2,230,856 - 4,541</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -24546,26 +24372,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G262" s="5" t="n">
-        <v>0.018124</v>
-      </c>
-      <c r="H262" s="5" t="n">
-        <v>0.129521</v>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J262" s="5" t="n">
+        <v>0.224185</v>
+      </c>
+      <c r="K262" s="5" t="n">
+        <v>-8.474354</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -24596,12 +24422,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Common Shares      Contributed  Reserve  Comprehen-                holders’</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Loan interest</t>
+          <t>Share-based payment – Iron Range 1,000,000</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -24610,29 +24436,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F263" s="5" t="n">
-        <v>0.011286</v>
-      </c>
-      <c r="G263" s="5" t="n">
-        <v>0.001475</v>
-      </c>
-      <c r="H263" s="5" t="n">
-        <v>0.005279</v>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J263" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -24663,41 +24491,45 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Common Shares      Contributed  Reserve  Comprehen-                holders’</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Non-flow through units issued 7,780,000 225,150</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
-      <c r="E264" s="5" t="n">
-        <v>0.096859</v>
-      </c>
-      <c r="F264" s="5" t="n">
-        <v>0.383947</v>
-      </c>
-      <c r="G264" s="5" t="n">
-        <v>-0.000666</v>
-      </c>
-      <c r="H264" s="5" t="n">
-        <v>0.218099</v>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J264" s="5" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>0.16385</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -24728,12 +24560,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Other comprehensive gain</t>
+          <t>Common Shares      Contributed  Reserve  Comprehen-                holders’</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Currency translation adjustment</t>
+          <t>Flow through units issued 4,990,000 142,315</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -24747,26 +24579,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G265" s="5" t="n">
-        <v>0.01071</v>
-      </c>
-      <c r="H265" s="5" t="n">
-        <v>0.067467</v>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J265" s="5" t="n">
+        <v>0.195908</v>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>0.053593</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -24797,12 +24629,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Other comprehensive gain</t>
+          <t>Common Shares      Contributed  Reserve  Comprehen-                holders’</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Total comprehensive loss</t>
+          <t>Warrants issued as finders’ fees</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -24816,26 +24648,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G266" s="5" t="n">
-        <v>0.384516</v>
-      </c>
-      <c r="H266" s="5" t="n">
-        <v>1.016127</v>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J266" s="5" t="n">
+        <v>0.008869</v>
+      </c>
+      <c r="K266" s="5" t="n">
+        <v>0.008869</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -24866,19 +24698,15 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Other comprehensive gain</t>
+          <t>Common Shares      Contributed  Reserve  Comprehen-                holders’</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Other financing costs (26,623)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -24889,26 +24717,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G267" s="5" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="H267" s="5" t="n">
-        <v>2e-08</v>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J267" s="5" t="n">
+        <v>-0.04217</v>
+      </c>
+      <c r="K267" s="5" t="n">
+        <v>-0.015548</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -24939,19 +24767,15 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Other comprehensive gain</t>
+          <t>Common Shares      Contributed  Reserve  Comprehen-                holders’</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Balance, March 31, 2015 45,951,490 6,873,984 2,632,071 - 12,422</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -24962,26 +24786,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G268" s="5" t="n">
-        <v>37.760237</v>
-      </c>
-      <c r="H268" s="5" t="n">
-        <v>49.357358</v>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J268" s="5" t="n">
+        <v>-0.026564</v>
+      </c>
+      <c r="K268" s="5" t="n">
+        <v>-9.545040999999999</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -25012,12 +24836,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Balance, April 1, 2010 37,760,237 4,486,812 1,304,767 - -</t>
+          <t>Corporate communications</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -25031,21 +24855,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G269" s="5" t="n">
-        <v>1.398104</v>
-      </c>
-      <c r="H269" s="5" t="n">
-        <v>-4.393475</v>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I269" s="5" t="n">
+        <v>0.014238</v>
+      </c>
+      <c r="J269" s="5" t="n">
+        <v>0.054527</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
@@ -25081,15 +24905,19 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Share-based payment</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>Foreign exchange (gain) / loss (note 14)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -25100,21 +24928,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G270" s="5" t="n">
-        <v>-0.000666</v>
-      </c>
-      <c r="H270" s="5" t="n">
-        <v>-0.000666</v>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I270" s="5" t="n">
+        <v>-0.200074</v>
+      </c>
+      <c r="J270" s="5" t="n">
+        <v>0.058284</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -25150,12 +24978,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Currency translation adjustment</t>
+          <t>Loan interest</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -25164,26 +24992,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F271" s="5" t="n">
+        <v>0.011286</v>
       </c>
       <c r="G271" s="5" t="n">
-        <v>0.01071</v>
+        <v>0.001475</v>
       </c>
       <c r="H271" s="5" t="n">
-        <v>0.01071</v>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.005279</v>
+      </c>
+      <c r="I271" s="5" t="n">
+        <v>0.00525</v>
+      </c>
+      <c r="J271" s="5" t="n">
+        <v>0.00525</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
@@ -25219,19 +25041,15 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss on debt settlement</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -25242,21 +25060,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G272" s="5" t="n">
-        <v>-0.395226</v>
-      </c>
-      <c r="H272" s="5" t="n">
-        <v>-0.395226</v>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J272" s="5" t="n">
+        <v>0.128886</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
@@ -25292,40 +25112,32 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2011 37,760,237 4,486,812 1,304,101 - 10,710</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E273" s="5" t="n">
+        <v>0.096859</v>
+      </c>
+      <c r="F273" s="5" t="n">
+        <v>0.383947</v>
       </c>
       <c r="G273" s="5" t="n">
-        <v>1.012922</v>
+        <v>-0.000666</v>
       </c>
       <c r="H273" s="5" t="n">
-        <v>-4.788701</v>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.218099</v>
+      </c>
+      <c r="I273" s="5" t="n">
+        <v>0.016947</v>
+      </c>
+      <c r="J273" s="5" t="n">
+        <v>0.04957</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
@@ -25361,15 +25173,19 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Issued for cash 10,000,000 576,000</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>Writedowns (Notes 4 and 6)</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>WriteDown</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -25380,21 +25196,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G274" s="5" t="n">
-        <v>0.8245</v>
-      </c>
-      <c r="H274" s="5" t="n">
-        <v>0.2485</v>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I274" s="5" t="n">
+        <v>1.363548</v>
+      </c>
+      <c r="J274" s="5" t="n">
+        <v>0.070966</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
@@ -25430,15 +25246,19 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Issued for loan payable settlement 1,093,750</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>Deferred income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -25449,21 +25269,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G275" s="5" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="H275" s="5" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I275" s="5" t="n">
+        <v>-0.003426</v>
+      </c>
+      <c r="J275" s="5" t="n">
+        <v>-0.022725</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
@@ -25499,12 +25319,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+          <t>Other comprehensive items</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Share-based payment – finders fee</t>
+          <t>Unrealized loss on investments available for sale</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -25518,21 +25338,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G276" s="5" t="n">
-        <v>0.009719999999999999</v>
-      </c>
-      <c r="H276" s="5" t="n">
-        <v>0.009719999999999999</v>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J276" s="5" t="n">
+        <v>0.018299</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
@@ -25568,15 +25390,19 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+          <t>Other comprehensive items</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Financing costs (12,442)</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>Basic and diluted loss per share (note 8)</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -25587,21 +25413,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G277" s="5" t="n">
-        <v>-0.01728</v>
-      </c>
-      <c r="H277" s="5" t="n">
-        <v>-0.004838</v>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I277" s="5" t="n">
+        <v>1.5e-07</v>
+      </c>
+      <c r="J277" s="5" t="n">
+        <v>4e-08</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
@@ -25637,15 +25463,19 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+          <t>Other comprehensive items</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding (note 8)</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -25656,21 +25486,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G278" s="5" t="n">
-        <v>0.304701</v>
-      </c>
-      <c r="H278" s="5" t="n">
-        <v>0.304701</v>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I278" s="5" t="n">
+        <v>11.047932</v>
+      </c>
+      <c r="J278" s="5" t="n">
+        <v>23.627543</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -25711,7 +25541,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Share-based payment – Ahbau Cr. 1,000,000</t>
+          <t>Balance, March 31, 2012 50,213,987 5,256,570 1,862,184 255,100 78,177</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -25726,20 +25556,16 @@
         </is>
       </c>
       <c r="G279" s="5" t="n">
-        <v>0.1</v>
+        <v>1.578736</v>
       </c>
       <c r="H279" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.578736</v>
+      </c>
+      <c r="I279" s="5" t="n">
+        <v>1.578736</v>
+      </c>
+      <c r="J279" s="5" t="n">
+        <v>-5.873295</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -25780,7 +25606,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Share-based payment – Cuyoaco 360,000</t>
+          <t>Share-based payment – Preston 300,000</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -25794,21 +25620,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G280" s="5" t="n">
-        <v>0.0432</v>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H280" s="5" t="n">
-        <v>0.0432</v>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.012</v>
+      </c>
+      <c r="I280" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="J280" s="5" t="n">
+        <v>0.012</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -25849,7 +25673,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Future share –based payment</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -25864,20 +25688,16 @@
         </is>
       </c>
       <c r="G281" s="5" t="n">
-        <v>0.1651</v>
+        <v>0.304701</v>
       </c>
       <c r="H281" s="5" t="n">
-        <v>0.1651</v>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.304701</v>
+      </c>
+      <c r="I281" s="5" t="n">
+        <v>0.016947</v>
+      </c>
+      <c r="J281" s="5" t="n">
+        <v>0.016947</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -25918,7 +25738,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Subscriptions received in advance</t>
+          <t>Share-based payment – Ahbau Cr. 1,000,000 100,000 65,100</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -25932,21 +25752,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G282" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H282" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I282" s="5" t="n">
+        <v>-0.1651</v>
+      </c>
+      <c r="J282" s="5" t="n">
+        <v>-0.1651</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -25987,7 +25807,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2012 50,213,987 5,256,570 1,862,184 255,100 78,177</t>
+          <t>Subscriptions received in advance</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -26002,20 +25822,16 @@
         </is>
       </c>
       <c r="G283" s="5" t="n">
-        <v>1.578736</v>
+        <v>0.09</v>
       </c>
       <c r="H283" s="5" t="n">
-        <v>-5.873295</v>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.09</v>
+      </c>
+      <c r="I283" s="5" t="n">
+        <v>0.153859</v>
+      </c>
+      <c r="J283" s="5" t="n">
+        <v>0.153859</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -26051,38 +25867,40 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Foreign exchange translation</t>
+          <t>Share consolidation 1-for-5</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
-      <c r="E284" s="5" t="n">
-        <v>0.025172</v>
-      </c>
-      <c r="F284" s="5" t="n">
-        <v>0.022211</v>
-      </c>
-      <c r="G284" s="5" t="n">
-        <v>0.00188</v>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I284" s="5" t="n">
+        <v>-41.21119</v>
+      </c>
+      <c r="J284" s="5" t="n">
+        <v>-41.21119</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -26118,40 +25936,38 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Write off of properties (note 4)</t>
+          <t>Units issued for cash 6,713,001 245,696</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
-      <c r="E285" s="5" t="n">
-        <v>0.062453</v>
-      </c>
-      <c r="F285" s="5" t="n">
-        <v>1.464415</v>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H285" s="5" t="n">
+        <v>0.40278</v>
+      </c>
+      <c r="I285" s="5" t="n">
+        <v>0.40278</v>
+      </c>
+      <c r="J285" s="5" t="n">
+        <v>0.157084</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -26187,37 +26003,35 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E286" s="5" t="n">
-        <v>-1.228262</v>
-      </c>
-      <c r="F286" s="5" t="n">
-        <v>-2.985228</v>
-      </c>
-      <c r="G286" s="5" t="n">
-        <v>0.379874</v>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Flow through shares issued for cash 1,183,000 70,980</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H286" s="5" t="n">
+        <v>0.07098</v>
+      </c>
+      <c r="I286" s="5" t="n">
+        <v>0.07098</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -26258,12 +26072,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Litigation settlement proceeds</t>
+          <t>Value of tax benefits transferred</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -26272,28 +26086,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F287" s="5" t="n">
-        <v>0.476878</v>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H287" s="5" t="n">
+        <v>-0.027864</v>
+      </c>
+      <c r="I287" s="5" t="n">
+        <v>-0.027864</v>
+      </c>
+      <c r="J287" s="5" t="n">
+        <v>-0.027864</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
@@ -26329,17 +26139,19 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Consulting income</t>
+          <t>Flow through shares issued for cash 1,670,000 100,200</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
-      <c r="E288" s="5" t="n">
-        <v>0.02516</v>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26351,15 +26163,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H288" s="5" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="I288" s="5" t="n">
+        <v>0.1002</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -26400,24 +26208,24 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E289" s="5" t="n">
-        <v>0.019518</v>
-      </c>
-      <c r="F289" s="5" t="n">
-        <v>9.1e-05</v>
+          <t>Warrants issued as finders’ fees</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -26429,15 +26237,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I289" s="5" t="n">
+        <v>0.018854</v>
+      </c>
+      <c r="J289" s="5" t="n">
+        <v>0.018854</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
@@ -26473,40 +26277,38 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Other items total</t>
+          <t>Financing costs (33,202)</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
-      <c r="E290" s="5" t="n">
-        <v>0.044678</v>
-      </c>
-      <c r="F290" s="5" t="n">
-        <v>0.476969</v>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H290" s="5" t="n">
+        <v>-0.042925</v>
+      </c>
+      <c r="I290" s="5" t="n">
+        <v>-0.042925</v>
+      </c>
+      <c r="J290" s="5" t="n">
+        <v>-0.009723000000000001</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
@@ -26542,42 +26344,36 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E291" s="5" t="n">
-        <v>-1.183584</v>
-      </c>
-      <c r="F291" s="5" t="n">
-        <v>-2.508259</v>
+          <t>Currency translation adjustment</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G291" s="5" t="n">
-        <v>-0.379874</v>
-      </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01071</v>
+      </c>
+      <c r="H291" s="5" t="n">
+        <v>0.067467</v>
+      </c>
+      <c r="I291" s="5" t="n">
+        <v>-0.116794</v>
+      </c>
+      <c r="J291" s="5" t="n">
+        <v>-0.116794</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -26613,38 +26409,44 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Deficit - Beginning of year</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr"/>
-      <c r="E292" s="5" t="n">
-        <v>-0.488919</v>
-      </c>
-      <c r="F292" s="5" t="n">
-        <v>-1.699606</v>
-      </c>
-      <c r="G292" s="5" t="n">
-        <v>-4.272977</v>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I292" s="5" t="n">
+        <v>-1.68008</v>
+      </c>
+      <c r="J292" s="5" t="n">
+        <v>-1.68008</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
@@ -26680,40 +26482,38 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Warrant expiry extension charge (note 5)</t>
+          <t>Balance, March 31, 2013 19,868,798 5,724,380 2,110,446 243,859 (38,617)</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
-      <c r="E293" s="5" t="n">
-        <v>-0.027103</v>
-      </c>
-      <c r="F293" s="5" t="n">
-        <v>-0.065112</v>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H293" s="5" t="n">
+        <v>0.486693</v>
+      </c>
+      <c r="I293" s="5" t="n">
+        <v>0.486693</v>
+      </c>
+      <c r="J293" s="5" t="n">
+        <v>-7.553375</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
@@ -26749,38 +26549,40 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Deficit - End of year</t>
+          <t>Debts to be settled with equity</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
-      <c r="E294" s="5" t="n">
-        <v>-1.699606</v>
-      </c>
-      <c r="F294" s="5" t="n">
-        <v>-4.272977</v>
-      </c>
-      <c r="G294" s="5" t="n">
-        <v>-4.652851</v>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I294" s="5" t="n">
+        <v>0.080176</v>
+      </c>
+      <c r="J294" s="5" t="n">
+        <v>0.080176</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -26816,42 +26618,40 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E295" s="5" t="n">
-        <v>-8e-08</v>
-      </c>
-      <c r="F295" s="5" t="n">
-        <v>-1e-07</v>
-      </c>
-      <c r="G295" s="5" t="n">
-        <v>-1e-08</v>
+          <t>Shares issued for debt settlement 4,680,692</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I295" s="5" t="n">
+        <v>0.280842</v>
+      </c>
+      <c r="J295" s="5" t="n">
+        <v>0.280842</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
@@ -26887,42 +26687,40 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E296" s="5" t="n">
-        <v>15.636851</v>
-      </c>
-      <c r="F296" s="5" t="n">
-        <v>26.390593</v>
-      </c>
-      <c r="G296" s="5" t="n">
-        <v>37.760237</v>
+          <t>Units issued for debt settlement 1,800,000 108,000</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I296" s="5" t="n">
+        <v>0.17208</v>
+      </c>
+      <c r="J296" s="5" t="n">
+        <v>0.06408</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -26958,12 +26756,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Litigation settlement proceeds (note 4)</t>
+          <t>Equity issued for reserve</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -26972,50 +26770,2966 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F297" s="5" t="n">
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I297" s="5" t="n">
+        <v>-0.324035</v>
+      </c>
+      <c r="J297" s="5" t="n">
+        <v>-0.324035</v>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Shares issued for GRIT investment 5,400,000</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I298" s="5" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="J298" s="5" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Shares issued as finder’s fee 432,000</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I299" s="5" t="n">
+        <v>0.02592</v>
+      </c>
+      <c r="J299" s="5" t="n">
+        <v>0.02592</v>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Share-based payment - options</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I300" s="5" t="n">
+        <v>0.05633</v>
+      </c>
+      <c r="J300" s="5" t="n">
+        <v>0.05633</v>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Other comprehensive items</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I301" s="5" t="n">
+        <v>0.043158</v>
+      </c>
+      <c r="J301" s="5" t="n">
+        <v>0.043158</v>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Balance, March 31, 2014 32,181,490 6,463,142 2,230,856 - 4,541</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I302" s="5" t="n">
+        <v>0.224185</v>
+      </c>
+      <c r="J302" s="5" t="n">
+        <v>-8.474354</v>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Foreign exchange translation (note 14)</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H303" s="5" t="n">
+        <v>0.129521</v>
+      </c>
+      <c r="I303" s="5" t="n">
+        <v>-0.200074</v>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Writedowns (Note 6)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>WriteDown</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I304" s="5" t="n">
+        <v>1.363548</v>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Other comprehensive gain (loss)</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Currency translation adjustment</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H305" s="5" t="n">
+        <v>0.067467</v>
+      </c>
+      <c r="I305" s="5" t="n">
+        <v>-0.116794</v>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Other comprehensive gain (loss)</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H306" s="5" t="n">
+        <v>1.017127</v>
+      </c>
+      <c r="I306" s="5" t="n">
+        <v>1.796874</v>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Other comprehensive gain (loss)</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share (note 8)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H307" s="5" t="n">
+        <v>1.1e-07</v>
+      </c>
+      <c r="I307" s="5" t="n">
+        <v>1.5e-07</v>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Other comprehensive gain (loss)</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding (note 8)</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H308" s="5" t="n">
+        <v>9.871472000000001</v>
+      </c>
+      <c r="I308" s="5" t="n">
+        <v>11.047932</v>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Balance, March 31, 2011 37,760,237 4,486,812 1,304,101 - 10,710</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G309" s="5" t="n">
+        <v>1.012922</v>
+      </c>
+      <c r="H309" s="5" t="n">
+        <v>1.012922</v>
+      </c>
+      <c r="I309" s="5" t="n">
+        <v>-4.788701</v>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Issued for cash 10,000,000 576,000</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G310" s="5" t="n">
+        <v>0.8245</v>
+      </c>
+      <c r="H310" s="5" t="n">
+        <v>0.8245</v>
+      </c>
+      <c r="I310" s="5" t="n">
+        <v>0.2485</v>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Issued for loan payable settlement 1,093,750</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G311" s="5" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="H311" s="5" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="I311" s="5" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Share-based payment – finders fee</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G312" s="5" t="n">
+        <v>0.009719999999999999</v>
+      </c>
+      <c r="H312" s="5" t="n">
+        <v>0.009719999999999999</v>
+      </c>
+      <c r="I312" s="5" t="n">
+        <v>0.009719999999999999</v>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Financing costs (12,442)</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G313" s="5" t="n">
+        <v>-0.01728</v>
+      </c>
+      <c r="H313" s="5" t="n">
+        <v>-0.01728</v>
+      </c>
+      <c r="I313" s="5" t="n">
+        <v>-0.004838</v>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Share-based payment – Ahbau Cr. 1,000,000</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G314" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H314" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I314" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Share-based payment – Cuyoaco 360,000</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G315" s="5" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="H315" s="5" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="I315" s="5" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Future share –based payment</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G316" s="5" t="n">
+        <v>0.1651</v>
+      </c>
+      <c r="H316" s="5" t="n">
+        <v>0.1651</v>
+      </c>
+      <c r="I316" s="5" t="n">
+        <v>0.1651</v>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="n">
+        <v>-0.395226</v>
+      </c>
+      <c r="H317" s="5" t="n">
+        <v>-1.084594</v>
+      </c>
+      <c r="I317" s="5" t="n">
+        <v>-1.084594</v>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Warrants issued as finders fees</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H318" s="5" t="n">
+        <v>0.018854</v>
+      </c>
+      <c r="I318" s="5" t="n">
+        <v>0.018854</v>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Foreign exchange translation (note 9)</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G319" s="5" t="n">
+        <v>0.018124</v>
+      </c>
+      <c r="H319" s="5" t="n">
+        <v>0.129521</v>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Other comprehensive gain</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Currency translation adjustment</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G320" s="5" t="n">
+        <v>0.01071</v>
+      </c>
+      <c r="H320" s="5" t="n">
+        <v>0.067467</v>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Other comprehensive gain</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G321" s="5" t="n">
+        <v>0.384516</v>
+      </c>
+      <c r="H321" s="5" t="n">
+        <v>1.016127</v>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Other comprehensive gain</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G322" s="5" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="H322" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Other comprehensive gain</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="n">
+        <v>37.760237</v>
+      </c>
+      <c r="H323" s="5" t="n">
+        <v>49.357358</v>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Balance, April 1, 2010 37,760,237 4,486,812 1,304,767 - -</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="n">
+        <v>1.398104</v>
+      </c>
+      <c r="H324" s="5" t="n">
+        <v>-4.393475</v>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Number    Amount     Surplus     Reserve   sive Income    Deficit       Equity</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Share-based payment</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G325" s="5" t="n">
+        <v>-0.000666</v>
+      </c>
+      <c r="H325" s="5" t="n">
+        <v>-0.000666</v>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Foreign exchange translation</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" s="5" t="n">
+        <v>0.025172</v>
+      </c>
+      <c r="F326" s="5" t="n">
+        <v>0.022211</v>
+      </c>
+      <c r="G326" s="5" t="n">
+        <v>0.00188</v>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Write off of properties (note 4)</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" s="5" t="n">
+        <v>0.062453</v>
+      </c>
+      <c r="F327" s="5" t="n">
+        <v>1.464415</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E328" s="5" t="n">
+        <v>-1.228262</v>
+      </c>
+      <c r="F328" s="5" t="n">
+        <v>-2.985228</v>
+      </c>
+      <c r="G328" s="5" t="n">
+        <v>0.379874</v>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Litigation settlement proceeds</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F329" s="5" t="n">
         <v>0.476878</v>
       </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O297" t="inlineStr">
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Consulting income</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" s="5" t="n">
+        <v>0.02516</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E331" s="5" t="n">
+        <v>0.019518</v>
+      </c>
+      <c r="F331" s="5" t="n">
+        <v>9.1e-05</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Other items total</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" s="5" t="n">
+        <v>0.044678</v>
+      </c>
+      <c r="F332" s="5" t="n">
+        <v>0.476969</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E333" s="5" t="n">
+        <v>-1.183584</v>
+      </c>
+      <c r="F333" s="5" t="n">
+        <v>-2.508259</v>
+      </c>
+      <c r="G333" s="5" t="n">
+        <v>-0.379874</v>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Deficit - Beginning of year</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" s="5" t="n">
+        <v>-0.488919</v>
+      </c>
+      <c r="F334" s="5" t="n">
+        <v>-1.699606</v>
+      </c>
+      <c r="G334" s="5" t="n">
+        <v>-4.272977</v>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Warrant expiry extension charge (note 5)</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" s="5" t="n">
+        <v>-0.027103</v>
+      </c>
+      <c r="F335" s="5" t="n">
+        <v>-0.065112</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Deficit - End of year</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" s="5" t="n">
+        <v>-1.699606</v>
+      </c>
+      <c r="F336" s="5" t="n">
+        <v>-4.272977</v>
+      </c>
+      <c r="G336" s="5" t="n">
+        <v>-4.652851</v>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E337" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="F337" s="5" t="n">
+        <v>-1e-07</v>
+      </c>
+      <c r="G337" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E338" s="5" t="n">
+        <v>15.636851</v>
+      </c>
+      <c r="F338" s="5" t="n">
+        <v>26.390593</v>
+      </c>
+      <c r="G338" s="5" t="n">
+        <v>37.760237</v>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Litigation settlement proceeds (note 4)</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F339" s="5" t="n">
+        <v>0.476878</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
         <is>
           <t>-</t>
         </is>
